--- a/data/trans_orig/DC-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/DC-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico en 2007</t>
+          <t>Población con dolor crónico en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>93451</t>
+          <t>93923</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>133208</t>
+          <t>131263</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>128050</t>
+          <t>129971</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>169294</t>
+          <t>170748</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>232821</t>
+          <t>234691</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>291668</t>
+          <t>290708</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,03%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>560804</t>
+          <t>562749</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>600561</t>
+          <t>600089</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>519057</t>
+          <t>517603</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>560301</t>
+          <t>558380</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>75,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1090695</t>
+          <t>1091655</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1149542</t>
+          <t>1147672</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>83,02%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>121461</t>
+          <t>118587</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>164628</t>
+          <t>164538</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>226512</t>
+          <t>224919</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>278746</t>
+          <t>280452</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>354696</t>
+          <t>355764</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>427218</t>
+          <t>427430</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,14%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>797172</t>
+          <t>797262</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>840339</t>
+          <t>843213</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>689647</t>
+          <t>687941</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>741881</t>
+          <t>743474</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1502975</t>
+          <t>1502763</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1575497</t>
+          <t>1574429</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>77,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>81,57%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>123119</t>
+          <t>124276</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>165223</t>
+          <t>167374</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>214529</t>
+          <t>214877</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>263635</t>
+          <t>265463</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>353572</t>
+          <t>353967</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>417154</t>
+          <t>418544</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,72%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>513286</t>
+          <t>511135</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>555390</t>
+          <t>554233</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>420206</t>
+          <t>418378</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>469312</t>
+          <t>468964</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>61,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,63%</t>
+          <t>68,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>945196</t>
+          <t>943806</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1008778</t>
+          <t>1008383</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>74,02%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>156217</t>
+          <t>155528</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>202804</t>
+          <t>200369</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>274306</t>
+          <t>274763</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>332589</t>
+          <t>332772</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>442416</t>
+          <t>440730</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>518181</t>
+          <t>515648</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,03%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>739418</t>
+          <t>741853</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>786005</t>
+          <t>786694</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>706023</t>
+          <t>705840</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>764306</t>
+          <t>763849</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>67,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1462653</t>
+          <t>1465186</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1538418</t>
+          <t>1540104</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>77,75%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>534641</t>
+          <t>532336</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>619071</t>
+          <t>618642</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>893553</t>
+          <t>887963</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>999137</t>
+          <t>995197</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1444561</t>
+          <t>1447744</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1583231</t>
+          <t>1578929</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,72%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2657472</t>
+          <t>2657901</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2741902</t>
+          <t>2744207</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2380060</t>
+          <t>2384000</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2485644</t>
+          <t>2491234</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>70,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5072510</t>
+          <t>5076812</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5211180</t>
+          <t>5207997</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>78,25%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico en 2012</t>
+          <t>Población con dolor crónico en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>70423</t>
+          <t>71047</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>104570</t>
+          <t>106352</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>155556</t>
+          <t>158047</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>205444</t>
+          <t>204494</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>235531</t>
+          <t>239240</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>296048</t>
+          <t>298921</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,34%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>598899</t>
+          <t>597117</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>633046</t>
+          <t>632422</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>491606</t>
+          <t>492556</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>541494</t>
+          <t>539003</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>70,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1104471</t>
+          <t>1101598</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1164988</t>
+          <t>1161279</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>82,92%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>96326</t>
+          <t>99044</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>141299</t>
+          <t>139655</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>202421</t>
+          <t>199480</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>256187</t>
+          <t>258581</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>311898</t>
+          <t>311284</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>384337</t>
+          <t>381404</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,6%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>876648</t>
+          <t>878292</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>921621</t>
+          <t>918903</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>775997</t>
+          <t>773603</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>829763</t>
+          <t>832704</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1665794</t>
+          <t>1668727</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1738233</t>
+          <t>1738847</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>84,82%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44111</t>
+          <t>44789</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>77590</t>
+          <t>76644</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>157997</t>
+          <t>155660</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>206151</t>
+          <t>206378</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>213007</t>
+          <t>211196</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>274081</t>
+          <t>272382</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,75%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>680033</t>
+          <t>680979</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>713512</t>
+          <t>712834</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>571023</t>
+          <t>570796</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>619177</t>
+          <t>621514</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,47%</t>
+          <t>73,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>79,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1260716</t>
+          <t>1262415</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1321790</t>
+          <t>1323601</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>86,24%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73328</t>
+          <t>72604</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>109673</t>
+          <t>110602</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>229261</t>
+          <t>231285</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>288943</t>
+          <t>286697</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>315360</t>
+          <t>314817</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>383597</t>
+          <t>384066</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,21%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>838066</t>
+          <t>837137</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>874411</t>
+          <t>875135</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>762958</t>
+          <t>765204</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>822640</t>
+          <t>820616</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>72,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1616043</t>
+          <t>1615574</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1684280</t>
+          <t>1684823</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>80,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>84,26%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>322100</t>
+          <t>321648</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>392294</t>
+          <t>393929</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>798128</t>
+          <t>795179</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>901736</t>
+          <t>899494</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1134634</t>
+          <t>1141083</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1266868</t>
+          <t>1274004</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,24%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3034485</t>
+          <t>3032850</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3104679</t>
+          <t>3105131</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2656573</t>
+          <t>2658815</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2760181</t>
+          <t>2763130</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5718220</t>
+          <t>5711084</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5850454</t>
+          <t>5844005</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,66%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico en 2016</t>
+          <t>Población con dolor crónico en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51684</t>
+          <t>52215</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>83624</t>
+          <t>82462</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>109581</t>
+          <t>109390</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>148151</t>
+          <t>150129</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>170070</t>
+          <t>167525</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>223208</t>
+          <t>221491</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,44%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>591176</t>
+          <t>592338</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>623116</t>
+          <t>622585</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>524688</t>
+          <t>522710</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>563258</t>
+          <t>563449</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1124431</t>
+          <t>1126148</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1177569</t>
+          <t>1180114</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,57%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>75460</t>
+          <t>74681</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>113786</t>
+          <t>110373</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>156921</t>
+          <t>154581</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>207589</t>
+          <t>206471</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>242704</t>
+          <t>240447</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>306631</t>
+          <t>304311</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,73%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>908645</t>
+          <t>912058</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>946971</t>
+          <t>947750</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>835324</t>
+          <t>836442</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>885992</t>
+          <t>888332</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1758713</t>
+          <t>1761033</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1822640</t>
+          <t>1824897</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,36%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>49781</t>
+          <t>49857</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>81014</t>
+          <t>80883</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>94581</t>
+          <t>95600</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>132533</t>
+          <t>134382</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>150324</t>
+          <t>152640</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>201477</t>
+          <t>203188</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,16%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>678538</t>
+          <t>678669</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>709771</t>
+          <t>709695</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>652478</t>
+          <t>650629</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>690430</t>
+          <t>689411</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1343086</t>
+          <t>1341375</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1394239</t>
+          <t>1391923</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,12%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>82034</t>
+          <t>81286</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>120234</t>
+          <t>120164</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>201616</t>
+          <t>200060</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>258881</t>
+          <t>253998</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>292256</t>
+          <t>294589</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>362874</t>
+          <t>363217</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,33%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>817333</t>
+          <t>817403</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>855533</t>
+          <t>856281</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>784898</t>
+          <t>789781</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>842163</t>
+          <t>843719</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1618472</t>
+          <t>1618129</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1689090</t>
+          <t>1686757</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,13%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>286053</t>
+          <t>287743</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>360552</t>
+          <t>357414</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>600473</t>
+          <t>606242</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>694991</t>
+          <t>705030</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>911753</t>
+          <t>915013</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1030591</t>
+          <t>1032720</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,88%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3033798</t>
+          <t>3036936</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3108297</t>
+          <t>3106607</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2849551</t>
+          <t>2839512</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2944069</t>
+          <t>2938300</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5908301</t>
+          <t>5906172</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6027139</t>
+          <t>6023879</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>86,81%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico en 2023</t>
+          <t>Población con dolor crónico en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>121811</t>
+          <t>120750</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>161808</t>
+          <t>161833</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>188980</t>
+          <t>201629</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>282332</t>
+          <t>283654</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>343643</t>
+          <t>353178</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>428565</t>
+          <t>430478</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,63%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>473633</t>
+          <t>473608</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>513630</t>
+          <t>514691</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>74,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>442998</t>
+          <t>441676</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>536350</t>
+          <t>523701</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>932207</t>
+          <t>930294</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1017129</t>
+          <t>1007594</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>68,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>74,05%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>102608</t>
+          <t>85811</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>241639</t>
+          <t>239086</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>347135</t>
+          <t>346859</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>399297</t>
+          <t>397321</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>370954</t>
+          <t>369348</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>637923</t>
+          <t>640125</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,75%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>951225</t>
+          <t>953778</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1090256</t>
+          <t>1107053</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>559354</t>
+          <t>561330</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>611516</t>
+          <t>611792</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>58,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1513593</t>
+          <t>1511391</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1780562</t>
+          <t>1782168</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,35%</t>
+          <t>70,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>82,83%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>137803</t>
+          <t>138997</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>186569</t>
+          <t>187019</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>355706</t>
+          <t>355512</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>695192</t>
+          <t>706130</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>500762</t>
+          <t>496490</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>989681</t>
+          <t>964261</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>58,87%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>518111</t>
+          <t>517661</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>566877</t>
+          <t>565683</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,52%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>238174</t>
+          <t>227236</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>577660</t>
+          <t>577854</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>648365</t>
+          <t>673785</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1137284</t>
+          <t>1141556</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>69,69%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>187569</t>
+          <t>189169</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>240707</t>
+          <t>237556</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>395960</t>
+          <t>395797</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>583018</t>
+          <t>577721</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>53,25%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>601405</t>
+          <t>599337</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>864231</t>
+          <t>826559</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>40,88%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>686124</t>
+          <t>689275</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>739262</t>
+          <t>737662</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>511914</t>
+          <t>517211</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>698972</t>
+          <t>699135</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>63,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1157532</t>
+          <t>1195204</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1420358</t>
+          <t>1422426</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,25%</t>
+          <t>59,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>70,36%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>558646</t>
+          <t>541691</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>774040</t>
+          <t>774077</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1402061</t>
+          <t>1405779</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1966429</t>
+          <t>1954309</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,97%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2040610</t>
+          <t>2046408</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2786276</t>
+          <t>2721471</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>37,95%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2685777</t>
+          <t>2685740</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2901171</t>
+          <t>2918126</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8079,7 +8079,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1745851</t>
+          <t>1757971</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2310219</t>
+          <t>2306501</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>62,23%</t>
+          <t>62,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4385821</t>
+          <t>4450626</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5131487</t>
+          <t>5125689</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,15%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>71,47%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/DC-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/DC-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>93923</t>
+          <t>92653</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>131263</t>
+          <t>132890</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>129971</t>
+          <t>128398</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>170748</t>
+          <t>171206</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>234691</t>
+          <t>231492</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>290708</t>
+          <t>288842</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,89%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>562749</t>
+          <t>561122</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>600089</t>
+          <t>601359</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>80,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>517603</t>
+          <t>517145</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>558380</t>
+          <t>559953</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>75,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>81,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1091655</t>
+          <t>1093521</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1147672</t>
+          <t>1150871</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>83,25%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>118587</t>
+          <t>118216</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>164538</t>
+          <t>163199</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>224919</t>
+          <t>225436</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>280452</t>
+          <t>279931</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>355764</t>
+          <t>356742</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>427430</t>
+          <t>431114</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,34%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>797262</t>
+          <t>798601</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>843213</t>
+          <t>843584</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>687941</t>
+          <t>688462</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>743474</t>
+          <t>742957</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>71,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1502763</t>
+          <t>1499079</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1574429</t>
+          <t>1573451</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,52%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>124276</t>
+          <t>125574</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>167374</t>
+          <t>169269</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>214877</t>
+          <t>213630</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>265463</t>
+          <t>263520</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>353967</t>
+          <t>353452</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>418544</t>
+          <t>418390</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,71%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>511135</t>
+          <t>509240</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>554233</t>
+          <t>552935</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>75,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>418378</t>
+          <t>420321</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>468964</t>
+          <t>470211</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,18%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>68,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>943806</t>
+          <t>943960</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1008383</t>
+          <t>1008898</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>74,06%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>155528</t>
+          <t>154105</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>200369</t>
+          <t>200088</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>274763</t>
+          <t>273250</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>332772</t>
+          <t>331016</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>440730</t>
+          <t>443044</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>515648</t>
+          <t>516801</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,09%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>741853</t>
+          <t>742134</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>786694</t>
+          <t>788117</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>705840</t>
+          <t>707596</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>763849</t>
+          <t>765362</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,55%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1465186</t>
+          <t>1464033</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1540104</t>
+          <t>1537790</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>77,63%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>532336</t>
+          <t>533223</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>618642</t>
+          <t>622922</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>887963</t>
+          <t>892353</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>995197</t>
+          <t>999527</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1447744</t>
+          <t>1439946</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1578929</t>
+          <t>1579800</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,74%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2657901</t>
+          <t>2653621</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2744207</t>
+          <t>2743320</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>80,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2384000</t>
+          <t>2379670</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2491234</t>
+          <t>2486844</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5076812</t>
+          <t>5075941</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5207997</t>
+          <t>5215795</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>78,37%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>71047</t>
+          <t>69766</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>106352</t>
+          <t>108133</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>158047</t>
+          <t>155989</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>204494</t>
+          <t>203157</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>239240</t>
+          <t>238166</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>298921</t>
+          <t>296599</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,18%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>597117</t>
+          <t>595336</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>632422</t>
+          <t>633703</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>492556</t>
+          <t>493893</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>539003</t>
+          <t>541061</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,66%</t>
+          <t>70,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1101598</t>
+          <t>1103920</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1161279</t>
+          <t>1162353</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>82,99%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>99044</t>
+          <t>96893</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>139655</t>
+          <t>140550</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>199480</t>
+          <t>198571</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>258581</t>
+          <t>256126</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>311284</t>
+          <t>314763</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>381404</t>
+          <t>383137</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,69%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>878292</t>
+          <t>877397</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>918903</t>
+          <t>921054</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>773603</t>
+          <t>776058</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>832704</t>
+          <t>833613</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>75,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1668727</t>
+          <t>1666994</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1738847</t>
+          <t>1735368</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>84,65%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44789</t>
+          <t>44190</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>76644</t>
+          <t>74895</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>155660</t>
+          <t>159957</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>206378</t>
+          <t>208043</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>211196</t>
+          <t>213448</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>272382</t>
+          <t>272181</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,73%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>680979</t>
+          <t>682728</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>712834</t>
+          <t>713433</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>570796</t>
+          <t>569131</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>621514</t>
+          <t>617217</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>73,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1262415</t>
+          <t>1262616</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1323601</t>
+          <t>1321349</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>86,09%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72604</t>
+          <t>74765</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>110602</t>
+          <t>111030</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>231285</t>
+          <t>229557</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>286697</t>
+          <t>283624</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>314817</t>
+          <t>314631</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>384066</t>
+          <t>382700</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,14%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>837137</t>
+          <t>836709</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>875135</t>
+          <t>872974</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>765204</t>
+          <t>768277</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>820616</t>
+          <t>822344</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1615574</t>
+          <t>1616940</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1684823</t>
+          <t>1685009</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>80,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>84,27%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>321648</t>
+          <t>315704</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>393929</t>
+          <t>391960</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>795179</t>
+          <t>795910</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>899494</t>
+          <t>895993</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1141083</t>
+          <t>1135931</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1274004</t>
+          <t>1268886</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,17%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3032850</t>
+          <t>3034819</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3105131</t>
+          <t>3111075</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2658815</t>
+          <t>2662316</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2763130</t>
+          <t>2762399</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>74,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5711084</t>
+          <t>5716202</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5844005</t>
+          <t>5849157</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>81,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,74%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>52215</t>
+          <t>52097</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>82462</t>
+          <t>81186</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>109390</t>
+          <t>107114</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>150129</t>
+          <t>149576</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>167525</t>
+          <t>172372</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>221491</t>
+          <t>223515</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,59%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>592338</t>
+          <t>593614</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>622585</t>
+          <t>622703</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>522710</t>
+          <t>523263</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>563449</t>
+          <t>565725</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1126148</t>
+          <t>1124124</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1180114</t>
+          <t>1175267</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,21%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>74681</t>
+          <t>73885</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>110373</t>
+          <t>111268</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>154581</t>
+          <t>155756</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>206471</t>
+          <t>208768</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>240447</t>
+          <t>241625</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>304311</t>
+          <t>305719</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,8%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>912058</t>
+          <t>911163</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>947750</t>
+          <t>948546</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>836442</t>
+          <t>834145</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>888332</t>
+          <t>887157</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1761033</t>
+          <t>1759625</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1824897</t>
+          <t>1823719</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,3%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>49857</t>
+          <t>49482</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>80883</t>
+          <t>79958</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>95600</t>
+          <t>93784</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>134382</t>
+          <t>136249</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>152640</t>
+          <t>153512</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>203188</t>
+          <t>205474</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,3%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>678669</t>
+          <t>679594</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>709695</t>
+          <t>710070</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>650629</t>
+          <t>648762</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>689411</t>
+          <t>691227</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1341375</t>
+          <t>1339089</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1391923</t>
+          <t>1391051</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,06%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>81286</t>
+          <t>83140</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>120164</t>
+          <t>121943</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>200060</t>
+          <t>201678</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>253998</t>
+          <t>257162</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>294589</t>
+          <t>294098</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>363217</t>
+          <t>363716</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,36%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>817403</t>
+          <t>815624</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>856281</t>
+          <t>854427</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>789781</t>
+          <t>786617</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>843719</t>
+          <t>842101</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1618129</t>
+          <t>1617630</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1686757</t>
+          <t>1687248</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>85,16%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>287743</t>
+          <t>289786</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>357414</t>
+          <t>359789</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>606242</t>
+          <t>604553</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>705030</t>
+          <t>701740</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>915013</t>
+          <t>920510</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1032720</t>
+          <t>1034593</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,91%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3036936</t>
+          <t>3034561</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3106607</t>
+          <t>3104564</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2839512</t>
+          <t>2842802</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2938300</t>
+          <t>2939989</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5906172</t>
+          <t>5904299</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6023879</t>
+          <t>6018382</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>86,73%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>141352</t>
+          <t>150793</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>120750</t>
+          <t>128808</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>161833</t>
+          <t>171843</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>255886</t>
+          <t>278434</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>201629</t>
+          <t>258811</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>283654</t>
+          <t>302660</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>397239</t>
+          <t>429226</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>353178</t>
+          <t>398620</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>430478</t>
+          <t>459842</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>32,27%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>494089</t>
+          <t>539917</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>473608</t>
+          <t>518867</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>514691</t>
+          <t>561902</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>78,17%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>81,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>469444</t>
+          <t>455746</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>441676</t>
+          <t>431520</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>523701</t>
+          <t>475369</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>58,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>64,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>963533</t>
+          <t>995663</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>930294</t>
+          <t>965047</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1007594</t>
+          <t>1026269</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>69,88%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>72,02%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>182735</t>
+          <t>200029</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>85811</t>
+          <t>174017</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>239086</t>
+          <t>229707</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>372361</t>
+          <t>417014</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>346859</t>
+          <t>386709</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>397321</t>
+          <t>444908</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>555097</t>
+          <t>617042</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>369348</t>
+          <t>579043</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>640125</t>
+          <t>658426</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>31,05%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1010129</t>
+          <t>848888</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>953778</t>
+          <t>819210</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1107053</t>
+          <t>874900</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>78,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>586290</t>
+          <t>654460</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>561330</t>
+          <t>626566</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>611792</t>
+          <t>684765</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>61,16%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>58,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1596419</t>
+          <t>1503349</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1511391</t>
+          <t>1461965</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1782168</t>
+          <t>1541348</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>70,9%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>72,69%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>161505</t>
+          <t>185488</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>138997</t>
+          <t>160289</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>187019</t>
+          <t>210558</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>493128</t>
+          <t>337368</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>355512</t>
+          <t>312167</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>706130</t>
+          <t>363720</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>44,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>654633</t>
+          <t>522856</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>496490</t>
+          <t>486415</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>964261</t>
+          <t>561778</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>34,78%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>543175</t>
+          <t>617585</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>517661</t>
+          <t>592515</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>565683</t>
+          <t>642784</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,46%</t>
+          <t>73,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>440238</t>
+          <t>474891</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>227236</t>
+          <t>448539</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>577854</t>
+          <t>500092</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>55,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>61,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>983413</t>
+          <t>1092476</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>673785</t>
+          <t>1053554</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1141556</t>
+          <t>1128917</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>67,63%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>65,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>69,89%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>213097</t>
+          <t>221100</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>189169</t>
+          <t>196150</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>237556</t>
+          <t>248833</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>450798</t>
+          <t>416051</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>395797</t>
+          <t>387335</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>577721</t>
+          <t>444279</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>663895</t>
+          <t>637151</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>599337</t>
+          <t>599861</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>826559</t>
+          <t>680959</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>32,29%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>713734</t>
+          <t>768962</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>689275</t>
+          <t>741229</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>737662</t>
+          <t>793912</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>74,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>644134</t>
+          <t>702990</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>517211</t>
+          <t>674762</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>699135</t>
+          <t>731706</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>60,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1357868</t>
+          <t>1471953</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1195204</t>
+          <t>1428145</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1422426</t>
+          <t>1509243</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>71,56%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>698690</t>
+          <t>757410</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>541691</t>
+          <t>706662</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>774077</t>
+          <t>812902</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1572173</t>
+          <t>1448866</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1405779</t>
+          <t>1396088</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1954309</t>
+          <t>1501379</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>2270863</t>
+          <t>2206276</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2046408</t>
+          <t>2131668</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2721471</t>
+          <t>2284908</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>31,43%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2761127</t>
+          <t>2775352</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2685740</t>
+          <t>2719860</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2918126</t>
+          <t>2826100</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2140107</t>
+          <t>2288088</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1757971</t>
+          <t>2235575</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2306501</t>
+          <t>2340866</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>59,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>4901234</t>
+          <t>5063440</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4450626</t>
+          <t>4984808</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5125689</t>
+          <t>5138048</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>68,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>70,68%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
